--- a/Somativa_1/Modelagem.xlsx
+++ b/Somativa_1/Modelagem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yurih\Documents\Projetos_Web\Web\Somativa_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F36DA5-E5F4-4342-B197-49BB060281A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DA5CEB-6FA3-42CD-82DE-67C54E291D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{52E89C6F-A9E0-43E2-A26D-F62E3174E4F5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>USUARIO</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>POSTO_TRABALHO_FK</t>
+  </si>
+  <si>
+    <t>DIA_LIVRE</t>
+  </si>
+  <si>
+    <t>BLOCO</t>
   </si>
 </sst>
 </file>
@@ -586,7 +592,7 @@
         <v>22</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
@@ -609,7 +615,7 @@
         <v>23</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
@@ -627,6 +633,9 @@
       </c>
       <c r="L6" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">

--- a/Somativa_1/Modelagem.xlsx
+++ b/Somativa_1/Modelagem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yurih\Documents\Projetos_Web\Web\Somativa_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DA5CEB-6FA3-42CD-82DE-67C54E291D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCA3912-AD58-4EC2-B7D5-E7420FF4C4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{52E89C6F-A9E0-43E2-A26D-F62E3174E4F5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{52E89C6F-A9E0-43E2-A26D-F62E3174E4F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>USUARIO</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>POSTO_TRABALHO_FK</t>
-  </si>
-  <si>
-    <t>DIA_LIVRE</t>
   </si>
   <si>
     <t>BLOCO</t>
@@ -592,7 +589,7 @@
         <v>22</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.3">
@@ -634,9 +631,7 @@
       <c r="L6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="N6" s="1"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">

--- a/Somativa_1/Modelagem.xlsx
+++ b/Somativa_1/Modelagem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yurih\Documents\Projetos_Web\Web\Somativa_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCA3912-AD58-4EC2-B7D5-E7420FF4C4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CEC3B2-D59E-4E34-B7CA-F5D6029C69BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{52E89C6F-A9E0-43E2-A26D-F62E3174E4F5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>USUARIO</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>BLOCO</t>
+  </si>
+  <si>
+    <t>MAO DE OBRA</t>
   </si>
 </sst>
 </file>
@@ -655,12 +658,15 @@
         <v>16</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
